--- a/src/outputs/TTFINAL-cleaned.xlsx
+++ b/src/outputs/TTFINAL-cleaned.xlsx
@@ -34,16 +34,16 @@
     <t>ME 274%MACHINE DESIGN PROJECT%Andoh Prince Yaw%ED2-ME%240%Computer Based%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%240</t>
   </si>
   <si>
-    <t>AERO 274%AEROSPACE DESIGN PROJECT II%Andoh Prince Yaw%ED2-AERO%75%%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%75</t>
-  </si>
-  <si>
-    <t>IE 274%SECOND YEAR DESIGN PROJECT%Andoh Prince Yaw%ED2-IND%80%%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%80</t>
-  </si>
-  <si>
-    <t>AME 274%AUTOMOTIVE DESIGN PROJECT%Andoh Prince Yaw%ED2-AUTO%82%%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%82</t>
-  </si>
-  <si>
-    <t>MME 274%MARINE ENGINEERING DESIGN PROJECT II%Andoh Prince Yaw%ED2-MARI%37%%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%37</t>
+    <t>AERO 274%AEROSPACE DESIGN PROJECT II%Andoh Prince Yaw%ED2-AERO%75%Computer Based%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%75</t>
+  </si>
+  <si>
+    <t>IE 274%SECOND YEAR DESIGN PROJECT%Andoh Prince Yaw%ED2-IND%80%Computer Based%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%80</t>
+  </si>
+  <si>
+    <t>AME 274%AUTOMOTIVE DESIGN PROJECT%Andoh Prince Yaw%ED2-AUTO%82%Computer Based%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%82</t>
+  </si>
+  <si>
+    <t>MME 274%MARINE ENGINEERING DESIGN PROJECT II%Andoh Prince Yaw%ED2-MARI%37%Computer Based%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%37</t>
   </si>
   <si>
     <t>PCE 450%PETROLEUM REFINING ENGINEERING%Kwao-Boateng Emmanuela%ED4-PCE%55%VSLA/303%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%35/20</t>
@@ -100,10 +100,10 @@
     <t>PHY 170%GENERAL PHYSICS%Boateng Cyril Dziedzorm%ED1-CHE%120%Computer Based%Tuesday, 18 August 2026%Session, 1 (8:30 AM - 10:30 AM)%120</t>
   </si>
   <si>
-    <t>PHY 170%GENERAL PHYSICS%Abavare Eric Kwabena Kyeh%ED1-PCE%56%%Tuesday, 18 August 2026%Session, 1 (8:30 AM - 10:30 AM)%56</t>
-  </si>
-  <si>
-    <t>PHY 170%GENERAL PHYSICS%Boateng Cyril Dziedzorm%ED1-PE%130%%Tuesday, 18 August 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
+    <t>PHY 170%GENERAL PHYSICS%Abavare Eric Kwabena Kyeh%ED1-PCE%56%Computer Based%Tuesday, 18 August 2026%Session, 1 (8:30 AM - 10:30 AM)%56</t>
+  </si>
+  <si>
+    <t>PHY 170%GENERAL PHYSICS%Boateng Cyril Dziedzorm%ED1-PE%130%Computer Based%Tuesday, 18 August 2026%Session, 1 (8:30 AM - 10:30 AM)%130</t>
   </si>
   <si>
     <t>MME 292%SEAMANSHIP%Larkai Francis Laako%ED2-MARI%37%PB020%Tuesday, 18 August 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
@@ -301,7 +301,7 @@
     <t>CE 164%CIVIL ENGINEERING DRAWING%Osei Jack Banahene%ED1-GEOL%125%Computer Based%Thursday, 20 August 2026%Session, 1 (8:30 AM - 10:30 AM)%125</t>
   </si>
   <si>
-    <t>ME 456%INTRODUCTION TO FINITE ELEMENT%Andoh Prince Yaw%ED4-AUTO%32%%Thursday, 20 August 2026%Session, 1 (8:30 AM - 10:30 AM)%32</t>
+    <t>ME 456%INTRODUCTION TO FINITE ELEMENT%Andoh Prince Yaw%ED4-AUTO%32%Computer Based%Thursday, 20 August 2026%Session, 1 (8:30 AM - 10:30 AM)%32</t>
   </si>
   <si>
     <t>ME 374%MACHINE DESIGN II%Afriyie Nyarko Frank Kwabena%ED3-AE%101%NAF1/EA/A110%Thursday, 20 August 2026%Session, 1 (8:30 AM - 10:30 AM)%41/30/30</t>
@@ -688,43 +688,43 @@
     <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-BME%80%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
   </si>
   <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-AUTO%82%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%82</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Reindorf Nartey Borkor%ED2-CE%250%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%250</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-PCE%65%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%65</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-PE%95%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-GEOM%132%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%132</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-MSE%83%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%83</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-METE%57%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%57</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-COE%255%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%255</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-GEOL%150%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%150</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-TEL%175%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%175</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-AE%155%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%155</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-AERO%75%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%75</t>
-  </si>
-  <si>
-    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-IND%80%%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-AUTO%82%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%82</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Reindorf Nartey Borkor%ED2-CE%250%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%250</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-PCE%65%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%65</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS OF SEVERAL VARIABLES%Eghan Rhydal Esi%ED2-PE%95%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%95</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-GEOM%132%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%132</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-MSE%83%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%83</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Asamoah Joshua Kiddy Kwasi%ED2-METE%57%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%57</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-COE%255%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%255</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-GEOL%150%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%150</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-TEL%175%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%175</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-AE%155%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%155</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-AERO%75%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%75</t>
+  </si>
+  <si>
+    <t>MATH 252%CALCULUS WITH SEVERAL VARIABLES%Wireko Fredrick Asenso%ED2-IND%80%Computer Based%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%80</t>
   </si>
   <si>
     <t>CHE 156%PHYSICAL CHEMISTRY FOR ENGINEERS%Anang Daniel Adjah%ED1-CHE%120%VSLA/303/LT/304%Wednesday, 26 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/30/25/20</t>
@@ -901,19 +901,19 @@
     <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-AERO%70%Computer Based%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%70</t>
   </si>
   <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-AE%128%%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-BME%136%%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%136</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Patricia Gustafson-Asamoah%ED1-CE%245%%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%245</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION  SKILLS II%Yeboah Philomena Ama Okyeso%ED1-CHE%120%%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%120</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Bernard Ampong%ED1-COE%262%%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%262</t>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-AE%128%Computer Based%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%128</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-BME%136%Computer Based%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%136</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Patricia Gustafson-Asamoah%ED1-CE%245%Computer Based%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%245</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION  SKILLS II%Yeboah Philomena Ama Okyeso%ED1-CHE%120%Computer Based%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%120</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Bernard Ampong%ED1-COE%262%Computer Based%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%262</t>
   </si>
   <si>
     <t>EE 262%AC MACHINES%Asigri Peter%ED2-EE%340%NEB-TF/NEB-SF%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%170/170</t>
@@ -940,22 +940,22 @@
     <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-PCE%56%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%56</t>
   </si>
   <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Sarfo-Adu Kwasi%ED1-AUTO%85%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%85</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-EE%295%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%295</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-IND%83%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%125</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-MSE%100%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOM%103%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%103</t>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Sarfo-Adu Kwasi%ED1-AUTO%85%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%85</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-EE%295%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%295</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-IND%83%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%125</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-MSE%100%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOM%103%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%103</t>
   </si>
   <si>
     <t>ME 492%MANAGEMENT AND ENTREPRENEURSHIP DEVELOPMENT%Aikins Stephen Hill Mends%ED4-COE%160%PB001/PB014/PB020/PB201/PB214%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%32/32/32/32/32</t>
@@ -994,16 +994,16 @@
     <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-MARI%46%Computer Based%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%46</t>
   </si>
   <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-ME%225%%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%225</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-PE%130%%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%130</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-TEL%130%%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%130</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-METE%75%%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%75</t>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-ME%225%Computer Based%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%225</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-PE%130%Computer Based%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%130</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-TEL%130%Computer Based%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%130</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-METE%75%Computer Based%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%75</t>
   </si>
   <si>
     <t>COE 272%DIGITAL SYSTEMS DESIGN I%Nunoo-Mensah Henry%ED2-BME%80%NEB-FF2/NEB-FF1%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%30/50</t>

--- a/src/outputs/TTFINAL-cleaned.xlsx
+++ b/src/outputs/TTFINAL-cleaned.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
   <si>
     <t>CHE 258%DRAWING FOR ENGINEERS%Darkwah Lawrence%ED2-CHE%160%VSLA/303/RMA/RMB/206/304%Monday, 17 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/30/22/22/22/20</t>
   </si>
@@ -73,7 +73,7 @@
     <t>CE 256%FLUID MECHANICS%Anornu Geophrey Kwame%ED2-CE%250%PB001/PB014/PB020/PB201/PB214/PB008/PB208/PB212%Monday, 17 August 2026%Session, 2 (12:00 PM - 2:00 PM)%36/36/36/36/36/25/25/20</t>
   </si>
   <si>
-    <t>ME 374%MACHINE ELEMENTS DESIGN II%Andoh Prince Yaw%ED3-ME%222%COMPUTER BASED%Monday, 17 August 2026%Session, 3 (3:00 PM - 5:00 PM)%222</t>
+    <t>ME 374%MACHINE ELEMENTS DESIGN II%Andoh Prince Yaw%ED3-ME%222%Computer Based%Monday, 17 August 2026%Session, 3 (3:00 PM - 5:00 PM)%222</t>
   </si>
   <si>
     <t>ME 464%INSTRUMENTATION%Adam Faisal Wahib%ED4-ME%135%VSLA/303/206/RMA/RMB%Monday, 17 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40/30/22/22/21</t>
@@ -805,28 +805,28 @@
     <t>GE 362%PRINCIPLES OF GIS%Forkuo Eric Kwabena%ED3-GEOM%122%NEB-FF1/NEB-FF2/NAF1%Wednesday, 26 August 2026%Session, 3 (3:00 PM - 5:00 PM)%50/30/42</t>
   </si>
   <si>
-    <t>GED 370%FOUNDATION ENGINEERING%Amenuvor Andrew Cudzo%ED3-GEOL%154%303/LT/RMA/RMB/304/VSLA%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%26/22/22/22/22/40</t>
-  </si>
-  <si>
-    <t>CE 360%FOUNDATION ENGINEERING%Acquaah Vincent Kofi Abaka%ED3-CE%230%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%36/36/36/36/36/25/25</t>
-  </si>
-  <si>
-    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-IND%80%NEB-FF1/NEB-FF2%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%50/30</t>
-  </si>
-  <si>
-    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-MARI%37%PB020 %Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%37</t>
-  </si>
-  <si>
-    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-AUTO%82%NAF1/EA/A110%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%32/25/25</t>
-  </si>
-  <si>
-    <t>CHE 250%STRENGTH OF MATERIALS FOR CHEMICAL ENGINEERS%Anang Daniel Adjah%ED2-CHE%160%VSLA/303/LT/RMA/RMB/304%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%45/30/25/21/21/20</t>
-  </si>
-  <si>
-    <t>EE 158%INTRO TO PYTHON &amp; COMPUTER NETWORKING%Charles Mawutor Adrah%ED1-EE%340%NEB-TF/NEB-SF%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%170/170</t>
-  </si>
-  <si>
-    <t>IE 366%ADVANCED MANUFACTURING TECHNOLOGY I%Takyi Gabriel%ED3-IND%70%NEB-FF2/NEB-FF1%Thursday, 27 August 2025%Session, 1 (8:30 AM - 10:30 AM)%25/45</t>
+    <t>GED 370%FOUNDATION ENGINEERING%Amenuvor Andrew Cudzo%ED3-GEOL%154%303/LT/RMA/RMB/304/VSLA%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%26/22/22/22/22/40</t>
+  </si>
+  <si>
+    <t>CE 360%FOUNDATION ENGINEERING%Acquaah Vincent Kofi Abaka%ED3-CE%230%PB001/PB014/PB020/PB201/PB214/PB008/PB208%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%36/36/36/36/36/25/25</t>
+  </si>
+  <si>
+    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-IND%80%NEB-FF1/NEB-FF2%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%50/30</t>
+  </si>
+  <si>
+    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-MARI%37%PB020 %Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
+  </si>
+  <si>
+    <t>ME 270%MANUFACTURING TECHNOLOGY%Boahen Samuel%ED2-AUTO%82%NAF1/EA/A110%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%32/25/25</t>
+  </si>
+  <si>
+    <t>CHE 250%STRENGTH OF MATERIALS FOR CHEMICAL ENGINEERS%Anang Daniel Adjah%ED2-CHE%160%VSLA/303/LT/RMA/RMB/304%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/30/25/21/21/20</t>
+  </si>
+  <si>
+    <t>EE 158%INTRO TO PYTHON &amp; COMPUTER NETWORKING%Charles Mawutor Adrah%ED1-EE%340%NEB-TF/NEB-SF%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%170/170</t>
+  </si>
+  <si>
+    <t>IE 366%ADVANCED MANUFACTURING TECHNOLOGY I%Takyi Gabriel%ED3-IND%70%NEB-FF2/NEB-FF1%Thursday, 27 August 2026%Session, 1 (8:30 AM - 10:30 AM)%25/45</t>
   </si>
   <si>
     <t>EE 188%ELECTRICAL MEASUREMENT AND INSTRUMENTATION%Obeng Kwakye Kingsford Sarkodie%ED1-TEL%130%VSLA/303/LT/RMA/RMB%Thursday, 27 August 2025%Session, 2 (12:00 PM - 2:00 PM)%40/30/20/20/20</t>
@@ -937,25 +937,25 @@
     <t>CHE 364%PACKAGING TECHNOLOGY%Baah-Ennumh Emmanuel Kwaku%ED3-CHE%45%VSLA/303%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%25/20</t>
   </si>
   <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-PCE%56%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%56</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Sarfo-Adu Kwasi%ED1-AUTO%85%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%85</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-EE%295%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%295</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-IND%83%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%125</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-MSE%100%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
-  </si>
-  <si>
-    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOM%103%Computer based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%103</t>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-PCE%56%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%56</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Sarfo-Adu Kwasi%ED1-AUTO%85%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%85</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-EE%295%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%295</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-IND%83%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%83</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOL%125%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%125</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Alhassan Yakubu%ED1-MSE%100%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%100</t>
+  </si>
+  <si>
+    <t>ENGL 158%COMMUNICATION SKILLS II%Yeboah Philomena Ama Okyeso%ED1-GEOM%103%Computer Based%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%103</t>
   </si>
   <si>
     <t>ME 492%MANAGEMENT AND ENTREPRENEURSHIP DEVELOPMENT%Aikins Stephen Hill Mends%ED4-COE%160%PB001/PB014/PB020/PB201/PB214%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%32/32/32/32/32</t>
@@ -1030,124 +1030,115 @@
     <t>CE 458%WATER RESOURCES ENGINEERING II%Anornu Geophrey Kwame%ED4-CE%105%NAF1/EA/A110%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%45/30/30</t>
   </si>
   <si>
-    <t>Monday, 31  August 2026%%%%%%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%Monday, 31  August 2026</t>
-  </si>
-  <si>
-    <t>ME 356%STRENGTH OF MATERIALS II%Tay Godwin Fabiola Kwaku%ED3-ME%222%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%76/76/45/25</t>
-  </si>
-  <si>
-    <t>METE 354%PHYSICAL METALLURGY OF NON-FERROUS METALS%Agyemang Frank Ofori%ED3-METE%87%PB001/PB020/PB014%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%35/30/22</t>
-  </si>
-  <si>
-    <t>TE 374%COMPUTER NETWORKING%Kwasi Adu-Boahen Opare%ED3-TEL%140%VSLA/LT/RMA/RMB/303/206%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%40/20/20/20/20/20</t>
-  </si>
-  <si>
-    <t>ME 162%BASIC MECHANICS%Oppong David Kofi%ED1-AE%128%NAF1/EA/A110/VCR%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/30/30/23</t>
-  </si>
-  <si>
-    <t>ME 162%BASIC MECHANICS%Oppong David Kofi%ED1-CHE%120%NEB-TF/NEB-SF%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%60/60</t>
-  </si>
-  <si>
-    <t>ME 164%STATICS OF SOLID MECHANICS%Oppong David Kofi%ED1-AUTO%85%VSLA/LT/RMA%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/20/20</t>
-  </si>
-  <si>
-    <t>PETE 450%NATURAL GAS ENGINEERING%Ankudey Emmanuel Godwin%ED3-PCE%53%RMB/303%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%23/30</t>
-  </si>
-  <si>
-    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-IND%80%NEB-FF1/NEB-FF2%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%50/30</t>
-  </si>
-  <si>
-    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-MARI%37%NAF1%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
-  </si>
-  <si>
-    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-ME%240%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%35/35/35/35/35/25/20/20</t>
-  </si>
-  <si>
-    <t>Monday, 31  August 2026%%%%%%Friday, 28 August 2026%Session, 1 (8:30 AM - 10:30 AM)%Monday, 31  August 2026</t>
-  </si>
-  <si>
-    <t>CHE 254%CHEMICAL ENGINEERING THERMODYNAMICS II%Eunice Sefakor Aku Dogbe%ED2-PCE%65%NEB-TF%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%65</t>
-  </si>
-  <si>
-    <t>PE 258%PETROLEUM ENGINEERING THERMODYNAMICS II%Sokama-Neuyam Yen Adams%ED2-PE%95%NAF1/EA/A110%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/30/25</t>
-  </si>
-  <si>
-    <t>GED 254%ROCK ENGINEERING%Gidigasu Solomon Senyo Robert%ED2-GEOL%150%VSLA/LT/RMA/RMB/303/206%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/22/22/22/24/20</t>
-  </si>
-  <si>
-    <t>ME 162%BASIC MECHANICS%Quansah David Ato%ED1-PE%130%NEB-TF/NEB-SF%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%70/60</t>
-  </si>
-  <si>
-    <t>ME 162%BASIC MECHANICS%Quansah David Ato%ED1-MSE%100%VSLA/LT/RMA/RMB%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/20/20/20</t>
-  </si>
-  <si>
-    <t>CE 352%STEEL AND TIMBER DESIGN%Mark Adom-Asamoah%ED3-CE%230%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/30/20/20/20</t>
-  </si>
-  <si>
-    <t>TE 468%MILLIMETERWAVE TECHNOLOGY%Abdul-Rahman Ahmed%ED4-TEL%33%NEB-FF2%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%33</t>
-  </si>
-  <si>
-    <t>IE 360%QUALITY ASSURANCE%Sackey Samuel Mensah%ED3-IND%70%NEB-SF%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%70</t>
-  </si>
-  <si>
-    <t>METE 252%METALLURGICAL RATE PROCESSES/SURFACE PHENOMENA%Patrick Aggrey%ED2-METE%57%NAF1/EA%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/17</t>
-  </si>
-  <si>
-    <t>CE 462%CONSTRUCTION MANAGEMENT%Obeng Daniel Atuah%ED4-CE%240%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/25/20/20</t>
-  </si>
-  <si>
-    <t>Monday, 31  August 2026%%%%%%Friday, 28 August 2026%Session, 2 (12:00 PM - 2:00 PM)%Monday, 31  August 2026</t>
-  </si>
-  <si>
-    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED2-EE%150%VSLA/LT/RMA/RMB/303/206%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40/22/22/22/24/20</t>
-  </si>
-  <si>
-    <t>ECON 152%ELEMENTS OF ECONOMICS II%Edward Yeboah%ED3-GEOM%15%LT%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%15</t>
-  </si>
-  <si>
-    <t>ECON 152%INTRODUCTION TO ECONOMICS II%Takyi Paul Owusu%ED1-CE%32%PB014%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%32</t>
-  </si>
-  <si>
-    <t>ECON 152%INTRODUCTORY ECONOMICS II%Beatrice Sarpong-Danquah%ED1-GEOL%30%PB201%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%30</t>
-  </si>
-  <si>
-    <t>ECON 152%ELEMENTS OF ECONOMICS II%Paul Owusu Takyi%ED2-BME%20%RMA%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%20</t>
-  </si>
-  <si>
-    <t>ECON 152%INTRODUCTION TO ECONOMICS II%Takyi Paul Owusu%ED2-COE%40%VSLA%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
-  </si>
-  <si>
-    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED2-TEL%30%PB001%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%30</t>
-  </si>
-  <si>
-    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED3-CHE%80%NEB-SF%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%80</t>
-  </si>
-  <si>
-    <t>ME 468%INTERNAL COMBUSTION ENGINES%Forson Francis Kofi%ED4-AERO%5%PB208%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%5</t>
-  </si>
-  <si>
-    <t>ME 468%INTERNAL COMBUSTION ENGINES%Forson Francis Kofi%ED4-ME%40%PB214%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
-  </si>
-  <si>
-    <t>PE 354%DRILLING ENGINEERING II%Erzuah Samuel%ED3-PE%80%NEB-SF%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%80</t>
-  </si>
-  <si>
-    <t>PE 474%PIPELINE ENGINEERING%Adjei Stephen%ED4-PE%99%NEB-TF%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%99</t>
-  </si>
-  <si>
-    <t>GED 466%PETROLEUM GEOLOGY%Foli Gordon%ED4-GEOL%35%PB020%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%35</t>
-  </si>
-  <si>
-    <t>BME 462%BIOMECHANICS II%Odame Prince%ED4-BME%87%NAF1/EA/A110%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%37/25/25</t>
-  </si>
-  <si>
-    <t>COE 382%DIGITAL COMPUTER DESIGN%Boateng Kwame Osei%ED3-EE%29%303%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%29</t>
-  </si>
-  <si>
-    <t>COE 372%DIGITAL SYSTEMS DESIGN II%Boateng Kwame Osei%ED3-COE%265%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%36/36/36/36/36/30/30/25</t>
-  </si>
-  <si>
-    <t>MSE 352%GLASS AND CEMENT TECHNOLOGIES%Andrews Anthony%ED3-MSE%85%NAF1/EA/A110%Friday, 28 August 2026%Session, 3 (3:00 PM - 5:00 PM)%37/25/23</t>
+    <t>ME 356%STRENGTH OF MATERIALS II%Tay Godwin Fabiola Kwaku%ED3-ME%222%NEB-TF/NEB-SF/NEB-FF1/NEB-FF2%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%76/76/45/25</t>
+  </si>
+  <si>
+    <t>METE 354%PHYSICAL METALLURGY OF NON-FERROUS METALS%Agyemang Frank Ofori%ED3-METE%87%PB001/PB020/PB014%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%35/30/22</t>
+  </si>
+  <si>
+    <t>TE 374%COMPUTER NETWORKING%Kwasi Adu-Boahen Opare%ED3-TEL%140%VSLA/LT/RMA/RMB/303/206%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%40/20/20/20/20/20</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Oppong David Kofi%ED1-AE%128%NAF1/EA/A110/VCR%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/30/30/23</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Oppong David Kofi%ED1-CHE%120%NEB-TF/NEB-SF%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%60/60</t>
+  </si>
+  <si>
+    <t>ME 164%STATICS OF SOLID MECHANICS%Oppong David Kofi%ED1-AUTO%85%VSLA/LT/RMA%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%45/20/20</t>
+  </si>
+  <si>
+    <t>PETE 450%NATURAL GAS ENGINEERING%Ankudey Emmanuel Godwin%ED3-PCE%53%RMB/303%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%23/30</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-IND%80%NEB-FF1/NEB-FF2%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%50/30</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-MARI%37%NAF1%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%37</t>
+  </si>
+  <si>
+    <t>ME 252%FLUID DYNAMICS I%Fiagbe Yesuenyeagbe Atsu Kwabla%ED2-ME%240%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Monday, 31 August 2026%Session, 1 (8:30 AM - 10:30 AM)%35/35/35/35/35/25/20/20</t>
+  </si>
+  <si>
+    <t>CHE 254%CHEMICAL ENGINEERING THERMODYNAMICS II%Eunice Sefakor Aku Dogbe%ED2-PCE%65%NEB-TF%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%65</t>
+  </si>
+  <si>
+    <t>PE 258%PETROLEUM ENGINEERING THERMODYNAMICS II%Sokama-Neuyam Yen Adams%ED2-PE%95%NAF1/EA/A110%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/30/25</t>
+  </si>
+  <si>
+    <t>GED 254%ROCK ENGINEERING%Gidigasu Solomon Senyo Robert%ED2-GEOL%150%VSLA/LT/RMA/RMB/303/206%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/22/22/22/24/20</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Quansah David Ato%ED1-PE%130%NEB-TF/NEB-SF%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%70/60</t>
+  </si>
+  <si>
+    <t>ME 162%BASIC MECHANICS%Quansah David Ato%ED1-MSE%100%VSLA/LT/RMA/RMB%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/20/20/20</t>
+  </si>
+  <si>
+    <t>CE 352%STEEL AND TIMBER DESIGN%Mark Adom-Asamoah%ED3-CE%230%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/30/20/20/20</t>
+  </si>
+  <si>
+    <t>TE 468%MILLIMETERWAVE TECHNOLOGY%Abdul-Rahman Ahmed%ED4-TEL%33%NEB-FF2%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%33</t>
+  </si>
+  <si>
+    <t>IE 360%QUALITY ASSURANCE%Sackey Samuel Mensah%ED3-IND%70%NEB-SF%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%70</t>
+  </si>
+  <si>
+    <t>METE 252%METALLURGICAL RATE PROCESSES/SURFACE PHENOMENA%Patrick Aggrey%ED2-METE%57%NAF1/EA%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%40/17</t>
+  </si>
+  <si>
+    <t>CE 462%CONSTRUCTION MANAGEMENT%Obeng Daniel Atuah%ED4-CE%240%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Monday, 31 August 2026%Session, 2 (12:00 PM - 2:00 PM)%35/35/35/35/35/25/20/20</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED2-EE%150%VSLA/LT/RMA/RMB/303/206%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40/22/22/22/24/20</t>
+  </si>
+  <si>
+    <t>ECON 152%ELEMENTS OF ECONOMICS II%Edward Yeboah%ED3-GEOM%15%LT%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%15</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTION TO ECONOMICS II%Takyi Paul Owusu%ED1-CE%32%PB014%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%32</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Beatrice Sarpong-Danquah%ED1-GEOL%30%PB201%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%30</t>
+  </si>
+  <si>
+    <t>ECON 152%ELEMENTS OF ECONOMICS II%Paul Owusu Takyi%ED2-BME%20%RMA%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%20</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTION TO ECONOMICS II%Takyi Paul Owusu%ED2-COE%40%VSLA%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED2-TEL%30%PB001%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%30</t>
+  </si>
+  <si>
+    <t>ECON 152%INTRODUCTORY ECONOMICS II%Takyi Paul Owusu%ED3-CHE%80%NEB-SF%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%80</t>
+  </si>
+  <si>
+    <t>ME 468%INTERNAL COMBUSTION ENGINES%Forson Francis Kofi%ED4-AERO%5%PB208%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%5</t>
+  </si>
+  <si>
+    <t>ME 468%INTERNAL COMBUSTION ENGINES%Forson Francis Kofi%ED4-ME%40%PB214%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%40</t>
+  </si>
+  <si>
+    <t>PE 354%DRILLING ENGINEERING II%Erzuah Samuel%ED3-PE%80%NEB-SF%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%80</t>
+  </si>
+  <si>
+    <t>PE 474%PIPELINE ENGINEERING%Adjei Stephen%ED4-PE%99%NEB-TF%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%99</t>
+  </si>
+  <si>
+    <t>GED 466%PETROLEUM GEOLOGY%Foli Gordon%ED4-GEOL%35%PB020%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%35</t>
+  </si>
+  <si>
+    <t>BME 462%BIOMECHANICS II%Odame Prince%ED4-BME%87%NAF1/EA/A110%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%37/25/25</t>
+  </si>
+  <si>
+    <t>COE 382%DIGITAL COMPUTER DESIGN%Boateng Kwame Osei%ED3-EE%29%303%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%29</t>
+  </si>
+  <si>
+    <t>COE 372%DIGITAL SYSTEMS DESIGN II%Boateng Kwame Osei%ED3-COE%265%PB001/PB020/PB014/PB201/PB214/PB008/PB208/PB212%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%36/36/36/36/36/30/30/25</t>
+  </si>
+  <si>
+    <t>MSE 352%GLASS AND CEMENT TECHNOLOGIES%Andrews Anthony%ED3-MSE%85%NAF1/EA/A110%Monday, 31 August 2026%Session, 3 (3:00 PM - 5:00 PM)%37/25/23</t>
   </si>
   <si>
     <t>ME 266%THERMODYNAMICS I%Amoabeng Kofi Owura%ED2-IND%80%PB001/PB014/PB020%Tuesday, 1 September 2026%Session, 1 (8:30 AM - 10:30 AM)%30/30/20</t>
@@ -1908,7 +1899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A507"/>
+  <dimension ref="A1:A504"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -4431,21 +4422,6 @@
         <v>503</v>
       </c>
     </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A506" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A507" t="s">
-        <v>506</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
